--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>5351497.79</v>
+        <v>6674206.73</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -4872,10 +4872,10 @@
         <v>19160355.68</v>
       </c>
       <c r="S32" t="n">
-        <v>16550727.08</v>
+        <v>16551308.69</v>
       </c>
       <c r="T32" t="n">
-        <v>16990873.17</v>
+        <v>16991454.78</v>
       </c>
       <c r="U32" t="n">
         <v>17886666.44</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1471182.28</v>
+        <v>1849537.42</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -14952,10 +14952,10 @@
         <v>18971</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>10598</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>10598</v>
       </c>
       <c r="U104" t="n">
         <v>10598</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -16483,19 +16483,19 @@
         <v>399585.19</v>
       </c>
       <c r="P115" t="n">
-        <v>560000</v>
+        <v>5437638.07</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>8863680.02</v>
+        <v>13741318.09</v>
       </c>
       <c r="S115" t="n">
-        <v>925621.71</v>
+        <v>996721.71</v>
       </c>
       <c r="T115" t="n">
-        <v>925621.71</v>
+        <v>996721.71</v>
       </c>
       <c r="U115" t="n">
         <v>8303680.02</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -17892,10 +17892,10 @@
         <v>889609.24</v>
       </c>
       <c r="S125" t="n">
-        <v>79099.03999999999</v>
+        <v>87026.24000000001</v>
       </c>
       <c r="T125" t="n">
-        <v>79099.03999999999</v>
+        <v>87026.24000000001</v>
       </c>
       <c r="U125" t="n">
         <v>364192.26</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -18163,7 +18163,7 @@
         <v>852219.98</v>
       </c>
       <c r="P127" t="n">
-        <v>2661868</v>
+        <v>2664461.33</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -18172,13 +18172,13 @@
         <v>6612696.72</v>
       </c>
       <c r="S127" t="n">
-        <v>2712899.82</v>
+        <v>2726699.82</v>
       </c>
       <c r="T127" t="n">
-        <v>2713219.82</v>
+        <v>2727019.82</v>
       </c>
       <c r="U127" t="n">
-        <v>3950828.72</v>
+        <v>3948235.39</v>
       </c>
       <c r="V127" t="n">
         <v>320</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3919200</v>
+        <v>4749200</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -20549,7 +20549,7 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>3979157.99</v>
+        <v>3979697.09</v>
       </c>
       <c r="S144" t="n">
         <v>2409038.89</v>
@@ -20558,7 +20558,7 @@
         <v>2502957.88</v>
       </c>
       <c r="U144" t="n">
-        <v>3235652.18</v>
+        <v>3236191.28</v>
       </c>
       <c r="V144" t="n">
         <v>93918.99000000001</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -21949,7 +21949,7 @@
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>5771532.08</v>
+        <v>5772340.73</v>
       </c>
       <c r="S154" t="n">
         <v>570925.76</v>
@@ -21958,7 +21958,7 @@
         <v>570925.76</v>
       </c>
       <c r="U154" t="n">
-        <v>5770981</v>
+        <v>5771789.65</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>
@@ -25151,7 +25151,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>27224747.91</v>
+        <v>29119533.31</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>01/06/2026 12:35:53</t>
+          <t>02/06/2026 09:58:37</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>60940.47</v>
+        <v>61510.47</v>
       </c>
       <c r="P6" t="n">
         <v>23626.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1372,10 +1372,10 @@
         <v>858923.46</v>
       </c>
       <c r="S7" t="n">
-        <v>267600.35</v>
+        <v>284205.35</v>
       </c>
       <c r="T7" t="n">
-        <v>372600.35</v>
+        <v>389205.35</v>
       </c>
       <c r="U7" t="n">
         <v>550795.47</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1503,13 +1503,13 @@
         <v>87272.24000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>186055.9</v>
+        <v>211055.9</v>
       </c>
       <c r="Q8" t="n">
         <v>57913</v>
       </c>
       <c r="R8" t="n">
-        <v>602021.4</v>
+        <v>627021.4</v>
       </c>
       <c r="S8" t="n">
         <v>348834.72</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2545319.67</v>
+        <v>2680964.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49337.3</v>
+        <v>67733.36</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -2772,10 +2772,10 @@
         <v>81465.10000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>33111.44</v>
+        <v>69900.72</v>
       </c>
       <c r="T17" t="n">
-        <v>33111.44</v>
+        <v>69900.72</v>
       </c>
       <c r="U17" t="n">
         <v>71456.17999999999</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4312,10 +4312,10 @@
         <v>744214.34</v>
       </c>
       <c r="S28" t="n">
-        <v>329040.58</v>
+        <v>472950.58</v>
       </c>
       <c r="T28" t="n">
-        <v>329040.58</v>
+        <v>472950.58</v>
       </c>
       <c r="U28" t="n">
         <v>606343.9399999999</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>659602.22</v>
+        <v>660552.37</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4592,10 +4592,10 @@
         <v>2212341.49</v>
       </c>
       <c r="S30" t="n">
-        <v>1656354.21</v>
+        <v>1689845.73</v>
       </c>
       <c r="T30" t="n">
-        <v>1770250.04</v>
+        <v>1803741.56</v>
       </c>
       <c r="U30" t="n">
         <v>1841672.04</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4813416.35</v>
+        <v>4855391.77</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>171270.71</v>
+        <v>201577.55</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1097192.23</v>
+        <v>1098662.94</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1334964.4</v>
+        <v>1345241.42</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>219000</v>
       </c>
       <c r="O46" t="n">
-        <v>71494.37</v>
+        <v>71578.10000000001</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>11125.84</v>
+        <v>14477.74</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>761377.5</v>
+        <v>1388103</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -8086,7 +8086,7 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1514015.72</v>
       </c>
       <c r="R55" t="n">
         <v>18253327.1</v>
@@ -8104,7 +8104,7 @@
         <v>5495750</v>
       </c>
       <c r="W55" t="n">
-        <v>18518759</v>
+        <v>20032774.72</v>
       </c>
       <c r="X55" t="n">
         <v>22965724</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>54000</v>
+        <v>563899.45</v>
       </c>
       <c r="R69" t="n">
         <v>680791.95</v>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>681657</v>
+        <v>1191556.45</v>
       </c>
       <c r="X69" t="n">
         <v>1226000</v>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
         <v>238607.79</v>
       </c>
       <c r="Q77" t="n">
-        <v>238608</v>
+        <v>478393</v>
       </c>
       <c r="R77" t="n">
         <v>1670666.79</v>
@@ -11184,7 +11184,7 @@
         <v>354819.03</v>
       </c>
       <c r="W77" t="n">
-        <v>1432059</v>
+        <v>1671844</v>
       </c>
       <c r="X77" t="n">
         <v>1671844</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -11312,10 +11312,10 @@
         <v>76897.66</v>
       </c>
       <c r="S78" t="n">
-        <v>59168.01</v>
+        <v>75773.00999999999</v>
       </c>
       <c r="T78" t="n">
-        <v>59168.01</v>
+        <v>75773.00999999999</v>
       </c>
       <c r="U78" t="n">
         <v>75773.00999999999</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>46241.32</v>
+        <v>61562.96</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -11589,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>410366.25</v>
+        <v>423756.71</v>
       </c>
       <c r="S80" t="n">
         <v>133147</v>
@@ -11598,7 +11598,7 @@
         <v>134497</v>
       </c>
       <c r="U80" t="n">
-        <v>406794.66</v>
+        <v>420185.12</v>
       </c>
       <c r="V80" t="n">
         <v>1350</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>268051</v>
       </c>
       <c r="R85" t="n">
         <v>1838981</v>
@@ -12304,7 +12304,7 @@
         <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1838981</v>
+        <v>2107032</v>
       </c>
       <c r="X85" t="n">
         <v>2107032</v>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2861229.41</v>
+        <v>2459898.9</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -14520,7 +14520,7 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>2861229.41</v>
+        <v>2459898.9</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>399585.19</v>
+        <v>501860.44</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -16492,16 +16492,16 @@
         <v>13741318.09</v>
       </c>
       <c r="S115" t="n">
-        <v>996721.71</v>
+        <v>1077721.71</v>
       </c>
       <c r="T115" t="n">
-        <v>996721.71</v>
+        <v>1082721.71</v>
       </c>
       <c r="U115" t="n">
         <v>8303680.02</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="W115" t="n">
         <v>8429440</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -16912,10 +16912,10 @@
         <v>83605</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>16605</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>16605</v>
       </c>
       <c r="U118" t="n">
         <v>83605</v>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>97447.12</v>
+        <v>128381.54</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -17883,13 +17883,13 @@
         <v>21712.72</v>
       </c>
       <c r="P125" t="n">
-        <v>525416.98</v>
+        <v>598000.64</v>
       </c>
       <c r="Q125" t="n">
         <v>8077</v>
       </c>
       <c r="R125" t="n">
-        <v>889609.24</v>
+        <v>947356.74</v>
       </c>
       <c r="S125" t="n">
         <v>87026.24000000001</v>
@@ -17898,7 +17898,7 @@
         <v>87026.24000000001</v>
       </c>
       <c r="U125" t="n">
-        <v>364192.26</v>
+        <v>349356.1</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -19709,7 +19709,7 @@
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -19718,7 +19718,7 @@
         <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -20132,10 +20132,10 @@
         <v>226677.94</v>
       </c>
       <c r="S141" t="n">
-        <v>143901.12</v>
+        <v>160506.12</v>
       </c>
       <c r="T141" t="n">
-        <v>145695.12</v>
+        <v>162300.12</v>
       </c>
       <c r="U141" t="n">
         <v>219030.12</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1063883.12</v>
+        <v>1092466.45</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21526,7 +21526,7 @@
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>127000</v>
+        <v>2986219</v>
       </c>
       <c r="R151" t="n">
         <v>3595409.87</v>
@@ -21544,7 +21544,7 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>3596273</v>
+        <v>6455492</v>
       </c>
       <c r="X151" t="n">
         <v>6455492</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21946,7 @@
         <v>551.08</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="R154" t="n">
         <v>5772340.73</v>
@@ -21964,7 +21964,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>5870981</v>
+        <v>10925362</v>
       </c>
       <c r="X154" t="n">
         <v>10925362</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -23632,10 +23632,10 @@
         <v>160562812.27</v>
       </c>
       <c r="S166" t="n">
-        <v>135266690.46</v>
+        <v>136851313.39</v>
       </c>
       <c r="T166" t="n">
-        <v>140706402.85</v>
+        <v>142291025.78</v>
       </c>
       <c r="U166" t="n">
         <v>139519212.18</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>30737969.69</v>
+        <v>30827969.69</v>
       </c>
       <c r="P170" t="n">
         <v>49898263.91</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>
@@ -25163,7 +25163,7 @@
         <v>26512660.49</v>
       </c>
       <c r="P177" t="n">
-        <v>4120579.53</v>
+        <v>4233962.27</v>
       </c>
       <c r="Q177" t="n">
         <v>0</v>
@@ -25172,13 +25172,13 @@
         <v>42504185.13</v>
       </c>
       <c r="S177" t="n">
-        <v>35701639.67</v>
+        <v>36361688.79</v>
       </c>
       <c r="T177" t="n">
-        <v>37314403.77</v>
+        <v>37974452.89</v>
       </c>
       <c r="U177" t="n">
-        <v>38383605.6</v>
+        <v>38270222.86</v>
       </c>
       <c r="V177" t="n">
         <v>1612764.1</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>02/06/2026 09:58:37</t>
+          <t>03/06/2026 10:28:59</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>14217.8</v>
+        <v>21522.2</v>
       </c>
       <c r="P7" t="n">
         <v>308127.99</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1780,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2233079.15</v>
+        <v>2240107.89</v>
       </c>
       <c r="P10" t="n">
-        <v>2025944.04</v>
+        <v>2104159.04</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>14260335.85</v>
+        <v>14272880.85</v>
       </c>
       <c r="S10" t="n">
         <v>8419823.18</v>
@@ -1798,7 +1798,7 @@
         <v>8555234.91</v>
       </c>
       <c r="U10" t="n">
-        <v>12234391.81</v>
+        <v>12168721.81</v>
       </c>
       <c r="V10" t="n">
         <v>135411.73</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>180019.94</v>
+        <v>181579.94</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -3180,16 +3180,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1456839.07</v>
+        <v>1869368.53</v>
       </c>
       <c r="P20" t="n">
-        <v>3188599.85</v>
+        <v>3273573.57</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8879223.73</v>
+        <v>8964197.449999999</v>
       </c>
       <c r="S20" t="n">
         <v>4824031.07</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>657501.1</v>
+        <v>659254.77</v>
       </c>
       <c r="P30" t="n">
-        <v>370669.45</v>
+        <v>372532.13</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
@@ -4592,16 +4592,16 @@
         <v>2212341.49</v>
       </c>
       <c r="S30" t="n">
-        <v>1689845.73</v>
+        <v>1654491.53</v>
       </c>
       <c r="T30" t="n">
         <v>1803741.56</v>
       </c>
       <c r="U30" t="n">
-        <v>1841672.04</v>
+        <v>1839809.36</v>
       </c>
       <c r="V30" t="n">
-        <v>113895.83</v>
+        <v>149250.03</v>
       </c>
       <c r="W30" t="n">
         <v>1841736</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3952238.66</v>
+        <v>4043127.4</v>
       </c>
       <c r="P32" t="n">
         <v>1273689.24</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>165425.92</v>
+        <v>169975.72</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>1263773.13</v>
+        <v>1282088.11</v>
       </c>
       <c r="P45" t="n">
         <v>983604</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8083,13 +8083,13 @@
         <v>761377.5</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="Q55" t="n">
         <v>1514015.72</v>
       </c>
       <c r="R55" t="n">
-        <v>18253327.1</v>
+        <v>25253327.1</v>
       </c>
       <c r="S55" t="n">
         <v>11054942.1</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9924,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X68" t="n">
         <v>0</v>
@@ -9936,7 +9936,7 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AB68" t="n">
         <v>5</v>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>609150</v>
+        <v>739350</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -10472,10 +10472,10 @@
         <v>921519</v>
       </c>
       <c r="S72" t="n">
-        <v>618450</v>
+        <v>748650</v>
       </c>
       <c r="T72" t="n">
-        <v>618450</v>
+        <v>748650</v>
       </c>
       <c r="U72" t="n">
         <v>921519</v>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>46172.22</v>
+        <v>46241.32</v>
       </c>
       <c r="P80" t="n">
         <v>3571.59</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2459898.9</v>
+        <v>2861229.41</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -16492,16 +16492,16 @@
         <v>13741318.09</v>
       </c>
       <c r="S115" t="n">
-        <v>1077721.71</v>
+        <v>1232621.71</v>
       </c>
       <c r="T115" t="n">
-        <v>1082721.71</v>
+        <v>1242621.71</v>
       </c>
       <c r="U115" t="n">
         <v>8303680.02</v>
       </c>
       <c r="V115" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="W115" t="n">
         <v>8429440</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -17180,7 +17180,7 @@
         <v>190000</v>
       </c>
       <c r="O120" t="n">
-        <v>96278.44</v>
+        <v>97447.12</v>
       </c>
       <c r="P120" t="n">
         <v>227316.91</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18160,7 @@
         <v>211572</v>
       </c>
       <c r="O127" t="n">
-        <v>852219.98</v>
+        <v>854484.87</v>
       </c>
       <c r="P127" t="n">
         <v>2664461.33</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -18717,7 +18717,7 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>308638.89</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -18729,7 +18729,7 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>308630.89</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -18738,13 +18738,13 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>308630.89</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>308638.89</v>
       </c>
       <c r="X131" t="n">
         <v>0</v>
@@ -18756,7 +18756,7 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>308638.89</v>
       </c>
       <c r="AB131" t="n">
         <v>5</v>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>652646.5600000001</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -18869,7 +18869,7 @@
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>652646.5600000001</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -18878,13 +18878,13 @@
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>652646.5600000001</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>652646.5600000001</v>
       </c>
       <c r="X132" t="n">
         <v>0</v>
@@ -18896,7 +18896,7 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>652646.5600000001</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -19304,7 +19304,7 @@
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="X135" t="n">
         <v>0</v>
@@ -19316,7 +19316,7 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>460000</v>
+        <v>560000</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -19724,7 +19724,7 @@
         <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>460000</v>
+        <v>560000</v>
       </c>
       <c r="X138" t="n">
         <v>0</v>
@@ -19736,7 +19736,7 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>460000</v>
+        <v>560000</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>1011239.26</v>
+        <v>1063763.32</v>
       </c>
       <c r="P144" t="n">
         <v>743505.8100000001</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -21940,7 +21940,7 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>132386.98</v>
+        <v>169085.7</v>
       </c>
       <c r="P154" t="n">
         <v>551.08</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="P157" t="n">
         <v>11400</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>91251027.70999999</v>
+        <v>99143374.3</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -24040,7 +24040,7 @@
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>36595939.71</v>
+        <v>38488734.91</v>
       </c>
       <c r="P169" t="n">
         <v>62818272</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>31847681.59</v>
+        <v>31937681.59</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>30827969.69</v>
+        <v>31217681.59</v>
       </c>
       <c r="P170" t="n">
         <v>49898263.91</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>
@@ -25163,22 +25163,22 @@
         <v>26512660.49</v>
       </c>
       <c r="P177" t="n">
-        <v>4233962.27</v>
+        <v>4360212.27</v>
       </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>42504185.13</v>
+        <v>42755513.13</v>
       </c>
       <c r="S177" t="n">
-        <v>36361688.79</v>
+        <v>36543438.79</v>
       </c>
       <c r="T177" t="n">
-        <v>37974452.89</v>
+        <v>38156202.89</v>
       </c>
       <c r="U177" t="n">
-        <v>38270222.86</v>
+        <v>38395300.86</v>
       </c>
       <c r="V177" t="n">
         <v>1612764.1</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>03/06/2026 10:28:59</t>
+          <t>04/06/2026 09:17:20</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -16492,16 +16492,16 @@
         <v>13741318.09</v>
       </c>
       <c r="S115" t="n">
-        <v>1232621.71</v>
+        <v>1325721.71</v>
       </c>
       <c r="T115" t="n">
-        <v>1242621.71</v>
+        <v>1336721.71</v>
       </c>
       <c r="U115" t="n">
         <v>8303680.02</v>
       </c>
       <c r="V115" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="W115" t="n">
         <v>8429440</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>1063763.32</v>
+        <v>1063883.12</v>
       </c>
       <c r="P144" t="n">
         <v>743505.8100000001</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -20680,7 +20680,7 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>327.92</v>
+        <v>368.19</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -21940,7 +21940,7 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>169085.7</v>
+        <v>169265.4</v>
       </c>
       <c r="P154" t="n">
         <v>551.08</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23620,7 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>90570908.59999999</v>
+        <v>90695404.40000001</v>
       </c>
       <c r="P166" t="n">
         <v>21043600.09</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -24040,7 +24040,7 @@
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>38488734.91</v>
+        <v>38702082.11</v>
       </c>
       <c r="P169" t="n">
         <v>62818272</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>31217681.59</v>
+        <v>31307681.59</v>
       </c>
       <c r="P170" t="n">
         <v>49898263.91</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>04/06/2026 09:17:20</t>
+          <t>05/06/2026 09:21:48</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2240107.89</v>
+        <v>2243166.49</v>
       </c>
       <c r="P10" t="n">
         <v>2104159.04</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>116000</v>
       </c>
       <c r="O11" t="n">
-        <v>48056.44</v>
+        <v>48131.44</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>659254.77</v>
+        <v>659351.59</v>
       </c>
       <c r="P30" t="n">
         <v>372532.13</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>122884.29</v>
+        <v>153936.68</v>
       </c>
       <c r="P79" t="n">
         <v>12692.75</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
         <v>564000</v>
       </c>
       <c r="O126" t="n">
-        <v>242961.36</v>
+        <v>323948.48</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18160,7 @@
         <v>211572</v>
       </c>
       <c r="O127" t="n">
-        <v>854484.87</v>
+        <v>875899.35</v>
       </c>
       <c r="P127" t="n">
         <v>2664461.33</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>19041664.7</v>
+        <v>20222134.92</v>
       </c>
       <c r="P140" t="n">
         <v>1425517.51</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23620,7 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>90695404.40000001</v>
+        <v>91220527.70999999</v>
       </c>
       <c r="P166" t="n">
         <v>21043600.09</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>31307681.59</v>
+        <v>31757681.59</v>
       </c>
       <c r="P170" t="n">
         <v>49898263.91</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>
@@ -25160,7 +25160,7 @@
         <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>26512660.49</v>
+        <v>27224747.91</v>
       </c>
       <c r="P177" t="n">
         <v>4360212.27</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>05/06/2026 09:21:48</t>
+          <t>06/06/2026 08:06:19</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>06/06/2026 08:06:19</t>
+          <t>07/06/2026 08:19:28</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>07/06/2026 08:19:28</t>
+          <t>08/06/2026 10:21:18</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>67683.7</v>
+        <v>68761.2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>858923.46</v>
+        <v>868462.78</v>
       </c>
       <c r="S7" t="n">
         <v>284205.35</v>
@@ -1378,7 +1378,7 @@
         <v>389205.35</v>
       </c>
       <c r="U7" t="n">
-        <v>550795.47</v>
+        <v>560334.79</v>
       </c>
       <c r="V7" t="n">
         <v>105000</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>88500.49000000001</v>
+        <v>91411.74000000001</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2680964.6</v>
+        <v>2741493.33</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>14272880.85</v>
       </c>
       <c r="S10" t="n">
-        <v>8419823.18</v>
+        <v>8432368.18</v>
       </c>
       <c r="T10" t="n">
-        <v>8555234.91</v>
+        <v>8567779.91</v>
       </c>
       <c r="U10" t="n">
         <v>12168721.81</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1884045.71</v>
+        <v>1894820.32</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3192,10 +3192,10 @@
         <v>8964197.449999999</v>
       </c>
       <c r="S20" t="n">
-        <v>4824031.07</v>
+        <v>5112239.69</v>
       </c>
       <c r="T20" t="n">
-        <v>4831031.1</v>
+        <v>5119239.72</v>
       </c>
       <c r="U20" t="n">
         <v>5690623.88</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13158.64</v>
+        <v>30728.92</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4309,7 +4309,7 @@
         <v>2308</v>
       </c>
       <c r="R28" t="n">
-        <v>744214.34</v>
+        <v>757054.3199999999</v>
       </c>
       <c r="S28" t="n">
         <v>472950.58</v>
@@ -4318,7 +4318,7 @@
         <v>472950.58</v>
       </c>
       <c r="U28" t="n">
-        <v>606343.9399999999</v>
+        <v>619183.92</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>660552.37</v>
+        <v>784065.47</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>659351.59</v>
       </c>
       <c r="P30" t="n">
-        <v>372532.13</v>
+        <v>374929.79</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
@@ -4592,16 +4592,16 @@
         <v>2212341.49</v>
       </c>
       <c r="S30" t="n">
-        <v>1654491.53</v>
+        <v>1650688.65</v>
       </c>
       <c r="T30" t="n">
         <v>1803741.56</v>
       </c>
       <c r="U30" t="n">
-        <v>1839809.36</v>
+        <v>1837411.7</v>
       </c>
       <c r="V30" t="n">
-        <v>149250.03</v>
+        <v>153052.91</v>
       </c>
       <c r="W30" t="n">
         <v>1841736</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4855391.77</v>
+        <v>5122497.08</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -5411,16 +5411,16 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1102319.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>1098662.94</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1097192.23</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>210635.23</v>
+        <v>213197.34</v>
       </c>
       <c r="S43" t="n">
         <v>50187</v>
@@ -6418,7 +6418,7 @@
         <v>54123</v>
       </c>
       <c r="U43" t="n">
-        <v>143635.23</v>
+        <v>146197.34</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>344369.67</v>
+        <v>459159.56</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1345241.42</v>
+        <v>1386775.36</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>72406.46000000001</v>
+        <v>86327.36</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11291,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>650.8099999999999</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -11309,7 +11309,7 @@
         <v>30045</v>
       </c>
       <c r="R78" t="n">
-        <v>76897.66</v>
+        <v>77358.83</v>
       </c>
       <c r="S78" t="n">
         <v>75773.00999999999</v>
@@ -11318,7 +11318,7 @@
         <v>75773.00999999999</v>
       </c>
       <c r="U78" t="n">
-        <v>75773.00999999999</v>
+        <v>76234.17999999999</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>3487177.25</v>
+        <v>7671789.91</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -16492,10 +16492,10 @@
         <v>13741318.09</v>
       </c>
       <c r="S115" t="n">
-        <v>1325721.71</v>
+        <v>1342221.71</v>
       </c>
       <c r="T115" t="n">
-        <v>1336721.71</v>
+        <v>1353221.71</v>
       </c>
       <c r="U115" t="n">
         <v>8303680.02</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>83605</v>
+        <v>87627.35000000001</v>
       </c>
       <c r="S118" t="n">
         <v>16605</v>
@@ -16918,7 +16918,7 @@
         <v>16605</v>
       </c>
       <c r="U118" t="n">
-        <v>83605</v>
+        <v>87627.35000000001</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>22040.72</v>
+        <v>23433.93</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>8077</v>
       </c>
       <c r="R125" t="n">
-        <v>947356.74</v>
+        <v>949486.34</v>
       </c>
       <c r="S125" t="n">
         <v>87026.24000000001</v>
@@ -17898,7 +17898,7 @@
         <v>87026.24000000001</v>
       </c>
       <c r="U125" t="n">
-        <v>349356.1</v>
+        <v>351485.7</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>904591.3</v>
+        <v>1079146.36</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -19429,7 +19429,7 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -19438,7 +19438,7 @@
         <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -20111,7 +20111,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>64653</v>
+        <v>65084</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -20129,7 +20129,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>226677.94</v>
+        <v>228416.15</v>
       </c>
       <c r="S141" t="n">
         <v>160506.12</v>
@@ -20138,7 +20138,7 @@
         <v>162300.12</v>
       </c>
       <c r="U141" t="n">
-        <v>219030.12</v>
+        <v>220768.33</v>
       </c>
       <c r="V141" t="n">
         <v>1794</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>370073.19</v>
+        <v>398680.41</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1092466.45</v>
+        <v>1112592.23</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>7800</v>
+        <v>9600</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>18190190.37</v>
+        <v>22752166.06</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>99143374.3</v>
+        <v>99266804.15000001</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -24031,7 +24031,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>40361270.91</v>
+        <v>42789520.91</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>31937681.59</v>
+        <v>32086720.48</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -24451,7 +24451,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>448000</v>
+        <v>560000</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>42755513.13</v>
+        <v>43217386.67</v>
       </c>
       <c r="S177" t="n">
         <v>36543438.79</v>
@@ -25178,7 +25178,7 @@
         <v>38156202.89</v>
       </c>
       <c r="U177" t="n">
-        <v>38395300.86</v>
+        <v>38857174.4</v>
       </c>
       <c r="V177" t="n">
         <v>1612764.1</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>08/06/2026 10:21:18</t>
+          <t>09/06/2026 09:18:07</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1229,16 +1229,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>86481.7</v>
+        <v>99525.98</v>
       </c>
       <c r="S6" t="n">
-        <v>62855.61</v>
+        <v>75899.89</v>
       </c>
       <c r="T6" t="n">
-        <v>79281.7</v>
+        <v>92325.98</v>
       </c>
       <c r="U6" t="n">
-        <v>62855.61</v>
+        <v>75899.89</v>
       </c>
       <c r="V6" t="n">
         <v>16426.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>86115.50999999999</v>
+        <v>114820.68</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1792,10 +1792,10 @@
         <v>14320448.76</v>
       </c>
       <c r="S10" t="n">
-        <v>8432368.18</v>
+        <v>8472368.18</v>
       </c>
       <c r="T10" t="n">
-        <v>8567779.91</v>
+        <v>8607779.91</v>
       </c>
       <c r="U10" t="n">
         <v>12216289.72</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>539416.15</v>
+        <v>713045.37</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>815133.6899999999</v>
+        <v>817531.87</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1346253.6</v>
+        <v>1795004.8</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5136145.93</v>
+        <v>5396153.86</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4872,16 +4872,16 @@
         <v>19160355.68</v>
       </c>
       <c r="S32" t="n">
-        <v>17186595.13</v>
+        <v>16551308.69</v>
       </c>
       <c r="T32" t="n">
-        <v>17626741.22</v>
+        <v>18094232.4</v>
       </c>
       <c r="U32" t="n">
         <v>17886666.44</v>
       </c>
       <c r="V32" t="n">
-        <v>440146.09</v>
+        <v>1542923.71</v>
       </c>
       <c r="W32" t="n">
         <v>17954344</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>66536.7</v>
+        <v>88715.60000000001</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1388103</v>
+        <v>3047728.5</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>153936.68</v>
+        <v>163845.72</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>19578.81</v>
+        <v>26105.08</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -16632,10 +16632,10 @@
         <v>13741318.09</v>
       </c>
       <c r="S116" t="n">
-        <v>1342221.71</v>
+        <v>1349321.71</v>
       </c>
       <c r="T116" t="n">
-        <v>1353221.71</v>
+        <v>1360321.71</v>
       </c>
       <c r="U116" t="n">
         <v>8303680.02</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -16891,7 +16891,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>19578.81</v>
+        <v>26105.08</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>86115.50999999999</v>
+        <v>114820.68</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>4749200</v>
+        <v>4720400</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -19980,7 +19980,7 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>4749200</v>
+        <v>4720400</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -19992,7 +19992,7 @@
         <v>8578400</v>
       </c>
       <c r="S140" t="n">
-        <v>4814000</v>
+        <v>4749200</v>
       </c>
       <c r="T140" t="n">
         <v>5593600</v>
@@ -20001,7 +20001,7 @@
         <v>8578400</v>
       </c>
       <c r="V140" t="n">
-        <v>779600</v>
+        <v>844400</v>
       </c>
       <c r="W140" t="n">
         <v>8578400</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>398680.41</v>
+        <v>493430.92</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -23751,7 +23751,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>99266804.15000001</v>
+        <v>99369076.87</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>32235279.66</v>
+        <v>32473208.21</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>10/06/2026 09:41:13</t>
+          <t>11/06/2026 09:56:32</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62855.61</v>
+        <v>75899.89</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>87272.24000000001</v>
+        <v>88500.49000000001</v>
       </c>
       <c r="P8" t="n">
         <v>211055.9</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2518346.77</v>
+        <v>2551898.07</v>
       </c>
       <c r="P10" t="n">
-        <v>2104159.04</v>
+        <v>2172425.7</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>8607779.91</v>
       </c>
       <c r="U10" t="n">
-        <v>12216289.72</v>
+        <v>12148023.06</v>
       </c>
       <c r="V10" t="n">
         <v>135411.73</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1869368.53</v>
+        <v>1884045.71</v>
       </c>
       <c r="P20" t="n">
         <v>3273573.57</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="P24" t="n">
         <v>68464.06</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>817531.87</v>
+        <v>818107.8199999999</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2212341.49</v>
+        <v>2212594.63</v>
       </c>
       <c r="S30" t="n">
         <v>1682515.64</v>
@@ -4598,7 +4598,7 @@
         <v>1837233.08</v>
       </c>
       <c r="U30" t="n">
-        <v>1835747.17</v>
+        <v>1836000.31</v>
       </c>
       <c r="V30" t="n">
         <v>154717.44</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
         <v>4851971.21</v>
       </c>
       <c r="P32" t="n">
-        <v>1273689.24</v>
+        <v>1441484.5</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -4872,13 +4872,13 @@
         <v>19160355.68</v>
       </c>
       <c r="S32" t="n">
-        <v>16551308.69</v>
+        <v>17018799.87</v>
       </c>
       <c r="T32" t="n">
-        <v>18094232.4</v>
+        <v>18561723.58</v>
       </c>
       <c r="U32" t="n">
-        <v>17886666.44</v>
+        <v>17718871.18</v>
       </c>
       <c r="V32" t="n">
         <v>1542923.71</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -5009,16 +5009,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>860517</v>
+        <v>970517</v>
       </c>
       <c r="S33" t="n">
-        <v>848517</v>
+        <v>919904.16</v>
       </c>
       <c r="T33" t="n">
-        <v>848517</v>
+        <v>919904.16</v>
       </c>
       <c r="U33" t="n">
-        <v>860517</v>
+        <v>970517</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>42156.29</v>
+        <v>55493.73</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>4434.28</v>
+        <v>4762.28</v>
       </c>
       <c r="P43" t="n">
         <v>67000</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>1325464.4</v>
+        <v>1334964.4</v>
       </c>
       <c r="P45" t="n">
         <v>983604</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>609150</v>
+        <v>739350</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -11032,10 +11032,10 @@
         <v>200000</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U76" t="n">
         <v>200000</v>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
         <v>40000</v>
       </c>
       <c r="O82" t="n">
-        <v>3528.45</v>
+        <v>3678.45</v>
       </c>
       <c r="P82" t="n">
         <v>450</v>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
         <v>50000</v>
       </c>
       <c r="O122" t="n">
-        <v>15638.58</v>
+        <v>16010.12</v>
       </c>
       <c r="P122" t="n">
         <v>2250</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18300,7 @@
         <v>211572</v>
       </c>
       <c r="O128" t="n">
-        <v>875899.35</v>
+        <v>904591.3</v>
       </c>
       <c r="P128" t="n">
         <v>2664461.33</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19712,10 +19712,10 @@
         <v>57000</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="U138" t="n">
         <v>57000</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
         <v>8578400</v>
       </c>
       <c r="S140" t="n">
-        <v>4749200</v>
+        <v>4720400</v>
       </c>
       <c r="T140" t="n">
         <v>5593600</v>
@@ -20001,7 +20001,7 @@
         <v>8578400</v>
       </c>
       <c r="V140" t="n">
-        <v>844400</v>
+        <v>873200</v>
       </c>
       <c r="W140" t="n">
         <v>8578400</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="P158" t="n">
         <v>11400</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -23760,7 +23760,7 @@
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>91227527.70999999</v>
+        <v>91251027.70999999</v>
       </c>
       <c r="P167" t="n">
         <v>21043600.09</v>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>32473208.21</v>
+        <v>32563208.21</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>
@@ -25300,25 +25300,25 @@
         <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>27224747.91</v>
+        <v>29119533.31</v>
       </c>
       <c r="P178" t="n">
-        <v>4413972.27</v>
+        <v>4621547.66</v>
       </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>43217386.67</v>
+        <v>43395308.51</v>
       </c>
       <c r="S178" t="n">
-        <v>36667468.79</v>
+        <v>36845390.63</v>
       </c>
       <c r="T178" t="n">
-        <v>38280232.89</v>
+        <v>38458154.73</v>
       </c>
       <c r="U178" t="n">
-        <v>38803414.4</v>
+        <v>38773760.85</v>
       </c>
       <c r="V178" t="n">
         <v>1612764.1</v>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>11/06/2026 09:56:32</t>
+          <t>12/06/2026 09:35:49</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202606.xlsx
+++ b/base_despesas/2026/despesas_202606.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>13/06/2026 08:28:32</t>
+          <t>14/06/2026 08:45:06</t>
         </is>
       </c>
     </row>
